--- a/data/Employee Darwin.xlsx
+++ b/data/Employee Darwin.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gommt-my.sharepoint.com/personal/mmt12354_go-mmt_com/Documents/Agent A Thon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{414827E6-8DDB-449E-8A99-51F9569A70EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4300760F-73E2-4F25-A437-2AA774725BD4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78796914-576A-44E8-9C76-8E2CC5940304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C07AD5D4-F130-4B08-B0F2-4774EA77DF00}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="295">
   <si>
     <t>EMP Code</t>
   </si>
@@ -92,6 +92,12 @@
     <t>Immediate Supervisor Code</t>
   </si>
   <si>
+    <t>Skip Manager</t>
+  </si>
+  <si>
+    <t>Skip Manager ID</t>
+  </si>
+  <si>
     <t>Past Exp In Years</t>
   </si>
   <si>
@@ -149,6 +155,12 @@
     <t>MMT12209</t>
   </si>
   <si>
+    <t>Himmat Shekhawat (MMT6679)</t>
+  </si>
+  <si>
+    <t>MMT6679</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
@@ -185,6 +197,12 @@
     <t>MMT12047</t>
   </si>
   <si>
+    <t>Vikram Yerra (MMT6616)</t>
+  </si>
+  <si>
+    <t>MMT6616</t>
+  </si>
+  <si>
     <t>Fresher</t>
   </si>
   <si>
@@ -248,6 +266,12 @@
     <t>MMT11043</t>
   </si>
   <si>
+    <t>Manish Sharma (MMT10620)</t>
+  </si>
+  <si>
+    <t>MMT10620</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
@@ -290,6 +314,12 @@
     <t>MMT11089</t>
   </si>
   <si>
+    <t>Ankit Gupta (MMT12754)</t>
+  </si>
+  <si>
+    <t>MMT12754</t>
+  </si>
+  <si>
     <t>MMT008</t>
   </si>
   <si>
@@ -308,6 +338,12 @@
     <t>MMT12206</t>
   </si>
   <si>
+    <t>Piyush Gupta (MMT5896)</t>
+  </si>
+  <si>
+    <t>MMT5896</t>
+  </si>
+  <si>
     <t>Coffee Day Beverages</t>
   </si>
   <si>
@@ -389,6 +425,9 @@
     <t>MMT12992</t>
   </si>
   <si>
+    <t>Dinesh Babu (MMT11043)</t>
+  </si>
+  <si>
     <t>Vodafone India</t>
   </si>
   <si>
@@ -431,6 +470,12 @@
     <t>MMT9677</t>
   </si>
   <si>
+    <t>HINA SRIVASTAVA (MMT10544)</t>
+  </si>
+  <si>
+    <t>MMT10544</t>
+  </si>
+  <si>
     <t>Uinvolve</t>
   </si>
   <si>
@@ -452,6 +497,12 @@
     <t>MMT12037</t>
   </si>
   <si>
+    <t>Abhishek Mishra (MMT7949)</t>
+  </si>
+  <si>
+    <t>MMT7949</t>
+  </si>
+  <si>
     <t>MG Motor India Pvt Ltd</t>
   </si>
   <si>
@@ -485,6 +536,12 @@
     <t>MMT11474</t>
   </si>
   <si>
+    <t>Manoj Yadav (MMT10963)</t>
+  </si>
+  <si>
+    <t>MMT10963</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
@@ -509,6 +566,12 @@
     <t>MMT12872</t>
   </si>
   <si>
+    <t>Anubhav Bansal (MMT12156)</t>
+  </si>
+  <si>
+    <t>MMT12156</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
@@ -557,6 +620,12 @@
     <t>MMT4154</t>
   </si>
   <si>
+    <t>Raviraj Patil (MMT13240)</t>
+  </si>
+  <si>
+    <t>MMT13240</t>
+  </si>
+  <si>
     <t>Delhivery Limited</t>
   </si>
   <si>
@@ -603,6 +672,12 @@
   </si>
   <si>
     <t>MMT5102</t>
+  </si>
+  <si>
+    <t>Harshit Kathuria (MMT5481)</t>
+  </si>
+  <si>
+    <t>MMT5481</t>
   </si>
   <si>
     <t>Trident Global Corp</t>
@@ -856,9 +931,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -915,7 +990,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1255,8 +1330,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7AAE51F-2A40-4FD6-87E0-282C8FF5449F}">
-  <dimension ref="A1:U45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:W45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1275,13 +1350,15 @@
     <col min="15" max="15" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="49.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.5703125" customWidth="1"/>
+    <col min="20" max="20" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1345,19 +1422,25 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2">
         <v>45383</v>
@@ -1366,63 +1449,69 @@
         <v>41995</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="E3" s="2">
         <v>45397</v>
@@ -1431,63 +1520,69 @@
         <v>45397</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>39</v>
-      </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2">
         <v>45383</v>
@@ -1496,63 +1591,69 @@
         <v>44599</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>39</v>
+      <c r="W4" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2">
         <v>45524</v>
@@ -1561,63 +1662,69 @@
         <v>45524</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="Q5" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2">
         <v>45383</v>
@@ -1626,63 +1733,69 @@
         <v>44861</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7" s="2">
         <v>45383</v>
@@ -1691,63 +1804,69 @@
         <v>45068</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="T7" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23">
       <c r="A8" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2">
         <v>45383</v>
@@ -1756,63 +1875,69 @@
         <v>44977</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2">
         <v>45677</v>
@@ -1821,63 +1946,69 @@
         <v>45677</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23">
       <c r="A10" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2">
         <v>45383</v>
@@ -1886,63 +2017,69 @@
         <v>43808</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="T10" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>39</v>
+        <v>63</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23">
       <c r="A11" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2">
         <v>45603</v>
@@ -1951,63 +2088,69 @@
         <v>45603</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23">
       <c r="A12" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E12" s="2">
         <v>45670</v>
@@ -2016,63 +2159,69 @@
         <v>45670</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E13" s="2">
         <v>45383</v>
@@ -2081,63 +2230,69 @@
         <v>43143</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>39</v>
+        <v>63</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23">
       <c r="A14" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E14" s="2">
         <v>45523</v>
@@ -2146,63 +2301,69 @@
         <v>45523</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23">
       <c r="A15" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E15" s="2">
         <v>45754</v>
@@ -2211,63 +2372,69 @@
         <v>45754</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>39</v>
+        <v>63</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23">
       <c r="A16" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E16" s="2">
         <v>45568</v>
@@ -2276,63 +2443,69 @@
         <v>45568</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>138</v>
+        <v>77</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23">
       <c r="A17" s="1" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E17" s="2">
         <v>45677</v>
@@ -2341,63 +2514,69 @@
         <v>45677</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23">
       <c r="A18" s="1" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2">
         <v>45666</v>
@@ -2406,63 +2585,69 @@
         <v>45666</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>138</v>
+        <v>168</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23">
       <c r="A19" s="1" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E19" s="2">
         <v>45747</v>
@@ -2471,63 +2656,69 @@
         <v>45747</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="Q19" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="W19" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="R19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>138</v>
-      </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23">
       <c r="A20" s="1" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E20" s="2">
         <v>45533</v>
@@ -2536,63 +2727,69 @@
         <v>45533</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23">
       <c r="A21" s="1" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2">
         <v>45719</v>
@@ -2601,63 +2798,69 @@
         <v>45719</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>39</v>
+        <v>181</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23">
       <c r="A22" s="1" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2">
         <v>45678</v>
@@ -2666,63 +2869,69 @@
         <v>45678</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>69</v>
+        <v>193</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>37</v>
+        <v>194</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23">
       <c r="A23" s="1" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E23" s="2">
         <v>45664</v>
@@ -2731,63 +2940,69 @@
         <v>45664</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="T23" s="1" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23">
       <c r="A24" s="1" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E24" s="2">
         <v>45383</v>
@@ -2796,63 +3011,69 @@
         <v>44781</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>61</v>
+        <v>175</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>69</v>
+        <v>176</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>182</v>
+        <v>67</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>138</v>
+        <v>77</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23">
       <c r="A25" s="1" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E25" s="2">
         <v>45694</v>
@@ -2861,63 +3082,69 @@
         <v>45694</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>56</v>
+        <v>211</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>36</v>
+        <v>212</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>189</v>
+        <v>40</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23">
       <c r="A26" s="1" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E26" s="2">
         <v>45155</v>
@@ -2926,63 +3153,69 @@
         <v>45155</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>56</v>
+        <v>211</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>196</v>
+        <v>62</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>189</v>
+        <v>181</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23">
       <c r="A27" s="1" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E27" s="2">
         <v>45607</v>
@@ -2991,63 +3224,69 @@
         <v>45607</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>189</v>
+        <v>114</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23">
       <c r="A28" s="1" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E28" s="2">
         <v>45701</v>
@@ -3056,63 +3295,69 @@
         <v>45701</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>189</v>
+        <v>114</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23">
       <c r="A29" s="1" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E29" s="2">
         <v>45504</v>
@@ -3121,63 +3366,69 @@
         <v>45504</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>69</v>
+        <v>212</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>189</v>
+        <v>77</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23">
       <c r="A30" s="1" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E30" s="2">
         <v>45582</v>
@@ -3186,63 +3437,69 @@
         <v>45582</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="Q30" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="R30" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="R30" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="S30" s="1" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>189</v>
+        <v>41</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23">
       <c r="A31" s="1" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E31" s="2">
         <v>44928</v>
@@ -3251,63 +3508,69 @@
         <v>44928</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>37</v>
+        <v>211</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>189</v>
+        <v>41</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23">
       <c r="A32" s="1" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E32" s="2">
         <v>45540</v>
@@ -3316,63 +3579,69 @@
         <v>45540</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="Q32" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="R32" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="R32" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="S32" s="1" t="s">
-        <v>61</v>
+        <v>212</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>189</v>
+        <v>67</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23">
       <c r="A33" s="1" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E33" s="2">
         <v>45659</v>
@@ -3381,63 +3650,69 @@
         <v>45659</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>221</v>
+        <v>63</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>138</v>
+        <v>40</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23">
       <c r="A34" s="1" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E34" s="2">
         <v>45754</v>
@@ -3446,63 +3721,69 @@
         <v>45754</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>138</v>
+        <v>62</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23">
       <c r="A35" s="1" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E35" s="2">
         <v>45258</v>
@@ -3511,63 +3792,69 @@
         <v>45258</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>138</v>
+        <v>41</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23">
       <c r="A36" s="1" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E36" s="2">
         <v>45684</v>
@@ -3576,63 +3863,69 @@
         <v>45684</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>39</v>
+        <v>181</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23">
       <c r="A37" s="1" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E37" s="2">
         <v>45799</v>
@@ -3641,63 +3934,69 @@
         <v>45799</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23">
       <c r="A38" s="1" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E38" s="2">
         <v>45383</v>
@@ -3706,63 +4005,69 @@
         <v>44844</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>39</v>
+        <v>167</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23">
       <c r="A39" s="1" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E39" s="2">
         <v>45782</v>
@@ -3771,63 +4076,69 @@
         <v>45782</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23">
       <c r="A40" s="1" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E40" s="2">
         <v>45670</v>
@@ -3836,63 +4147,69 @@
         <v>45670</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23">
       <c r="A41" s="1" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E41" s="2">
         <v>45761</v>
@@ -3901,63 +4218,69 @@
         <v>45761</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23">
       <c r="A42" s="1" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E42" s="2">
         <v>45726</v>
@@ -3966,63 +4289,69 @@
         <v>45726</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23">
       <c r="A43" s="1" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E43" s="2">
         <v>45946</v>
@@ -4031,63 +4360,69 @@
         <v>45946</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>37</v>
+        <v>194</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>258</v>
+        <v>114</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23">
       <c r="A44" s="1" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E44" s="2">
         <v>45911</v>
@@ -4096,63 +4431,69 @@
         <v>45911</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>39</v>
+        <v>181</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23">
       <c r="A45" s="1" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E45" s="2">
         <v>45670</v>
@@ -4161,49 +4502,55 @@
         <v>45670</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
